--- a/booking_forms/004_dance_class_booking_form--booking_forms.xlsx
+++ b/booking_forms/004_dance_class_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,12 +765,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -798,12 +798,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'8:00-9:00_am'}</t>
+          <t>8:00-9:00_am</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '8:00-9:00 am'}</t>
+          <t>8:00-9:00 am</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'9:00-10:00_am'}</t>
+          <t>9:00-10:00_am</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '9:00-10:00 am'}</t>
+          <t>9:00-10:00 am</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'10:00-11:00_am'}</t>
+          <t>10:00-11:00_am</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '10:00-11:00 am'}</t>
+          <t>10:00-11:00 am</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'11:00_am-12:00_pm'}</t>
+          <t>11:00_am-12:00_pm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '11:00 am-12:00 pm'}</t>
+          <t>11:00 am-12:00 pm</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'12:00-1:00_pm'}</t>
+          <t>12:00-1:00_pm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '12:00-1:00 pm'}</t>
+          <t>12:00-1:00 pm</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1:00-2:00_pm'}</t>
+          <t>1:00-2:00_pm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1:00-2:00 pm'}</t>
+          <t>1:00-2:00 pm</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2:00-3:00_pm'}</t>
+          <t>2:00-3:00_pm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2:00-3:00 pm'}</t>
+          <t>2:00-3:00 pm</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3:00-4:00_pm'}</t>
+          <t>3:00-4:00_pm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3:00-4:00 pm'}</t>
+          <t>3:00-4:00 pm</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'4:00-5:00_pm'}</t>
+          <t>4:00-5:00_pm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '4:00-5:00 pm'}</t>
+          <t>4:00-5:00 pm</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'5:00-6:00_pm'}</t>
+          <t>5:00-6:00_pm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '5:00-6:00 pm'}</t>
+          <t>5:00-6:00 pm</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'6:00-7:00_pm'}</t>
+          <t>6:00-7:00_pm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '6:00-7:00 pm'}</t>
+          <t>6:00-7:00 pm</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'7:00-8:00_pm'}</t>
+          <t>7:00-8:00_pm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '7:00-8:00 pm'}</t>
+          <t>7:00-8:00 pm</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'8:00-9:00_pm'}</t>
+          <t>8:00-9:00_pm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '8:00-9:00 pm'}</t>
+          <t>8:00-9:00 pm</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_1'}</t>
+          <t>instructor_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 1'}</t>
+          <t>Instructor 1</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_2'}</t>
+          <t>instructor_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 2'}</t>
+          <t>Instructor 2</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_3'}</t>
+          <t>instructor_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 3'}</t>
+          <t>Instructor 3</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_4'}</t>
+          <t>instructor_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 4'}</t>
+          <t>Instructor 4</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_5'}</t>
+          <t>instructor_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 5'}</t>
+          <t>Instructor 5</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_6'}</t>
+          <t>instructor_6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 6'}</t>
+          <t>Instructor 6</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_7'}</t>
+          <t>instructor_7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 7'}</t>
+          <t>Instructor 7</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_8'}</t>
+          <t>instructor_8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 8'}</t>
+          <t>Instructor 8</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_9'}</t>
+          <t>instructor_9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 9'}</t>
+          <t>Instructor 9</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_10'}</t>
+          <t>instructor_10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 10'}</t>
+          <t>Instructor 10</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_11'}</t>
+          <t>instructor_11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 11'}</t>
+          <t>Instructor 11</t>
         </is>
       </c>
     </row>
@@ -1206,29 +1206,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_12'}</t>
+          <t>instructor_12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 12'}</t>
+          <t>Instructor 12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>instructor_info_choices</t>
+          <t>class_instructor_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_12'}</t>
+          <t>instructor_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 12'}</t>
+          <t>Instructor 1</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_1'}</t>
+          <t>instructor_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 1'}</t>
+          <t>Instructor 2</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_2'}</t>
+          <t>instructor_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 2'}</t>
+          <t>Instructor 3</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_3'}</t>
+          <t>instructor_4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 3'}</t>
+          <t>Instructor 4</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_4'}</t>
+          <t>instructor_5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 4'}</t>
+          <t>Instructor 5</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_5'}</t>
+          <t>instructor_6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 5'}</t>
+          <t>Instructor 6</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_6'}</t>
+          <t>instructor_7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 6'}</t>
+          <t>Instructor 7</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_7'}</t>
+          <t>instructor_8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 7'}</t>
+          <t>Instructor 8</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_8'}</t>
+          <t>instructor_9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 8'}</t>
+          <t>Instructor 9</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_9'}</t>
+          <t>instructor_10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 9'}</t>
+          <t>Instructor 10</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_10'}</t>
+          <t>instructor_11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 10'}</t>
+          <t>Instructor 11</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1410,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_11'}</t>
+          <t>instructor_12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 11'}</t>
+          <t>Instructor 12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>class_instructor_choices</t>
+          <t>student_level_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'instructor_12'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Instructor 12'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'beginner'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1478,29 +1478,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'advanced'}</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced'}</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>student_level_choices</t>
+          <t>class_type_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'expert'}</t>
+          <t>ballet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Expert'}</t>
+          <t>Ballet</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'ballet'}</t>
+          <t>ballroom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Ballet'}</t>
+          <t>Ballroom</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'ballroom'}</t>
+          <t>hip-hop</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Ballroom'}</t>
+          <t>Hip-Hop</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'hip-hop'}</t>
+          <t>contemporary</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Hip-Hop'}</t>
+          <t>Contemporary</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'contemporary'}</t>
+          <t>latin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Contemporary'}</t>
+          <t>Latin</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'latin'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Latin'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'jazz'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Jazz'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1631,46 +1631,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>class_type_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'label':_'tap'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'label': 'Tap'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>class_type_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'label':_'tap'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'label': 'Tap'}</t>
+          <t>Tap</t>
         </is>
       </c>
     </row>
